--- a/data/trans_camb/IP16A04-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,78</t>
+          <t>0,0; 17,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,69</t>
+          <t>0,0; 15,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,24</t>
+          <t>0,0; 7,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,03</t>
+          <t>0,0; 9,52</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,77</t>
+          <t>0,0; 9,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,94</t>
+          <t>0,0; 7,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,72</t>
+          <t>0,0; 15,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,33</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,56</t>
+          <t>0,0; 6,74</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-37,7; 0,0</t>
+          <t>-37,4; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 18,35</t>
+          <t>-25,35; 16,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 0,0</t>
+          <t>-19,48; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 8,33</t>
+          <t>-12,72; 8,61</t>
         </is>
       </c>
     </row>
@@ -1104,27 +1104,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,95</t>
+          <t>0,0; 7,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-28,32; 0,0</t>
+          <t>-27,75; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 0,0</t>
+          <t>-28,61; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 0,0</t>
+          <t>-14,03; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 0,83</t>
+          <t>-12,8; 0,82</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 0,0</t>
+          <t>-36,53; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-37,31; 0,0</t>
+          <t>-38,37; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 0,0</t>
+          <t>-21,32; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 0,0</t>
+          <t>-21,27; 0,0</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,23</t>
+          <t>0,0; 22,5</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,79</t>
+          <t>0,0; 22,05</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,97; 15,21</t>
+          <t>1,94; 17,39</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,17</t>
+          <t>0,0; 9,18</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,28</t>
+          <t>0,0; 11,41</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,97</t>
+          <t>0,0; 5,94</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,13</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,34</t>
+          <t>-3,53; 0,34</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,95</t>
+          <t>-1,14; 3,85</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,01</t>
+          <t>-3,05; 1,15</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,39</t>
+          <t>-3,08; 1,34</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,45</t>
+          <t>-2,26; 0,41</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,98</t>
+          <t>-1,26; 1,98</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,66; —</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-91,97; 170,12</t>
+          <t>-92,22; 206,83</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-66,95; 438,74</t>
+          <t>-66,48; 384,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A04-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Provincia-trans_camb.xlsx
@@ -636,12 +636,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,53</t>
+          <t>0,0; 16,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,91</t>
+          <t>0,0; 13,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,27</t>
+          <t>0,0; 9,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,52</t>
+          <t>0,0; 6,66</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,94</t>
+          <t>0,0; 7,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,39</t>
+          <t>0,0; 8,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,38</t>
+          <t>0,0; 17,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,12</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>0,0; 8,37</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-37,4; 0,0</t>
+          <t>-37,93; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 16,26</t>
+          <t>-23,68; 19,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 0,0</t>
+          <t>-20,39; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 8,61</t>
+          <t>-12,87; 9,87</t>
         </is>
       </c>
     </row>
@@ -1104,27 +1104,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>0,0; 7,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-27,75; 0,0</t>
+          <t>-30,03; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 0,0</t>
+          <t>-27,87; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 0,0</t>
+          <t>-15,3; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 0,82</t>
+          <t>-13,87; 0,83</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 0,0</t>
+          <t>-36,83; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-38,37; 0,0</t>
+          <t>-38,03; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 0,0</t>
+          <t>-21,02; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 0,0</t>
+          <t>-17,1; 0,0</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,5</t>
+          <t>0,0; 23,57</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,05</t>
+          <t>0,0; 20,16</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,94; 17,39</t>
+          <t>1,95; 17,47</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,18</t>
+          <t>0,0; 8,55</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,41</t>
+          <t>0,0; 11,96</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 5,12</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,34</t>
+          <t>-3,26; 0,34</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,85</t>
+          <t>-1,16; 4,04</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1,15</t>
+          <t>-2,95; 1,17</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,34</t>
+          <t>-3,08; 1,32</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,41</t>
+          <t>-2,25; 0,41</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,98</t>
+          <t>-1,36; 2,12</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-73,66; —</t>
+          <t>-72,99; —</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-92,22; 206,83</t>
+          <t>-91,48; 139,35</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-66,48; 384,29</t>
+          <t>-66,56; 419,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A04-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Provincia-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes</t>
+          <t>Menores que consumieron medicamentos laxantes</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>3,16</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,61</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 13,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 18,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,11</t>
+          <t>0,0; 7,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,66</t>
+          <t>0,0; 7,03</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,63</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,08</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>1,9</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,63</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,08</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,84</t>
+          <t>0,0; 7,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 15,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,33</t>
+          <t>0,0; 9,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 6,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,37</t>
+          <t>0,0; 7,56</t>
         </is>
       </c>
     </row>
@@ -830,17 +830,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-12,35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-5,28</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 19,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-37,7; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-24,67; 18,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 0,0</t>
+          <t>-20,44; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 9,87</t>
+          <t>-13,12; 8,33</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-42,75%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-9,05</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-9,05</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1,53</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-9,05</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-9,05</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-28,32; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>-29,26; 0,0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>0,0; 7,95</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-30,03; 0,0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-27,87; 0,0</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 0,0</t>
+          <t>-14,17; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 0,83</t>
+          <t>-12,61; 0,83</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-8,93</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-8,93</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-8,93</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-8,93</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-36,9; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-37,31; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-36,83; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-38,03; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-21,02; 0,0</t>
+          <t>-18,12; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 0,0</t>
+          <t>-17,79; 0,0</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>4,67</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>7,82</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4,67</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,57</t>
+          <t>0,0; 23,79</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,16</t>
+          <t>0,0; 30,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,95; 17,47</t>
+          <t>1,97; 15,21</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>2,32</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>2,07</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 14,28</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,17</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,18</t>
+          <t>0,0; 4,97</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,12</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,54</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,59</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>-0,81</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1,33</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,34</t>
+          <t>-3,29; 1,01</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,04</t>
+          <t>-3,08; 1,39</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,17</t>
+          <t>-3,47; 0,34</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,32</t>
+          <t>-1,12; 3,95</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,41</t>
+          <t>-2,36; 0,45</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,12</t>
+          <t>-1,29; 1,98</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-35,54%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-39,07%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>-70,73%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>116,23%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-35,54%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-39,07%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-72,99; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-91,48; 139,35</t>
+          <t>-91,97; 170,12</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-66,56; 419,99</t>
+          <t>-66,95; 438,74</t>
         </is>
       </c>
     </row>
